--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>461 h</t>
+          <t>468 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L16" s="14" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>219.1</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>87.64</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="36">
@@ -5813,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>1375.2</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>305.6</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="72">
@@ -11267,7 +11267,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -13258,7 +13258,7 @@
         <v>36445.07</v>
       </c>
       <c r="P180" s="18" t="n">
-        <v>126</v>
+        <v>123.33</v>
       </c>
     </row>
   </sheetData>
@@ -13450,7 +13450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13476,7 +13476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 5 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 6 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13753,73 +13753,126 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-32732</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LA SENTINELLE</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32739</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>00163790</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
           <t>PDMDEP-32152</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-32159</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>00160662</t>
         </is>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K10" s="15" t="n">
         <v>1711.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr"/>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="18" t="n">
-        <v>6601.5</v>
+      <c r="B11" s="17" t="inlineStr"/>
+      <c r="C11" s="17" t="inlineStr"/>
+      <c r="D11" s="17" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="17" t="inlineStr"/>
+      <c r="J11" s="17" t="inlineStr"/>
+      <c r="K11" s="18" t="n">
+        <v>7416.5</v>
       </c>
     </row>
   </sheetData>
@@ -13830,6 +13883,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14304,7 +14358,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>159.75</v>
+        <v>161</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>33.25</v>
@@ -14313,7 +14367,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>196</v>
+        <v>197.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>49.75</v>
@@ -14323,7 +14377,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -14334,16 +14388,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>84.75</v>
+        <v>88.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>6.25</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>91.5</v>
+        <v>96.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>18.75</v>
@@ -14353,7 +14407,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>468 h</t>
+          <t>474 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3877,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>203.5</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>135.67</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="45">
@@ -11061,7 +11061,7 @@
         <v>15</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="L145" s="11" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>36445.07</v>
       </c>
       <c r="P180" s="18" t="n">
-        <v>123.33</v>
+        <v>121.89</v>
       </c>
     </row>
   </sheetData>
@@ -14358,7 +14358,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>161</v>
+        <v>162.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>33.25</v>
@@ -14367,7 +14367,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>197.25</v>
+        <v>198.75</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>49.75</v>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -14388,7 +14388,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>88.25</v>
+        <v>90.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>6.25</v>
@@ -14397,7 +14397,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>18.75</v>
@@ -14407,7 +14407,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>99.83</v>
+        <v>101.83</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>40,330 €</t>
+          <t>48,924 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,14 +769,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>11,049 €</t>
+          <t>18,010 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>29,281 €</t>
+          <t>30,914 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P180"/>
+  <dimension ref="A1:P184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2894,10 +2894,10 @@
         <v>1242.9</v>
       </c>
       <c r="O30" s="17" t="n">
-        <v>497.16</v>
+        <v>621.45</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>55.24</v>
+        <v>69.05</v>
       </c>
     </row>
     <row r="31">
@@ -3398,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>532.4</v>
+        <v>865.15</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>64.53</v>
+        <v>104.87</v>
       </c>
     </row>
     <row r="38">
@@ -4118,10 +4118,10 @@
         <v>1416</v>
       </c>
       <c r="O47" s="17" t="n">
-        <v>0</v>
+        <v>849.6</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>0</v>
+        <v>485.49</v>
       </c>
     </row>
     <row r="48">
@@ -4767,32 +4767,32 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
@@ -4818,19 +4818,19 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>149</v>
+        <v>533.8049999999999</v>
       </c>
       <c r="P57" s="13" t="n">
         <v>0</v>
@@ -4839,32 +4839,32 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4874,35 +4874,35 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>625</v>
-      </c>
-      <c r="O58" s="17" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>149</v>
       </c>
       <c r="P58" s="16" t="n">
         <v>0</v>
@@ -4962,48 +4962,48 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="O59" s="17" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33203</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5023,64 +5023,64 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166553</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>224</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33203</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[CD 38] - LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5090,64 +5090,64 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33207</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166553</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>3621</v>
+        <v>0</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>4224.5</v>
+        <v>0</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>469.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5167,64 +5167,64 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>1618.5</v>
+        <v>3621</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>1996.15</v>
+        <v>4224.5</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>499.04</v>
+        <v>469.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5234,69 +5234,69 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O63" s="17" t="n">
-        <v>0</v>
+        <v>1618.5</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>1996.15</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>0</v>
+        <v>499.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
@@ -5318,22 +5318,22 @@
         <v>3</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5343,27 +5343,27 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32902</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMANDE PAX </t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
@@ -5394,48 +5394,48 @@
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32910</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00159637</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P65" s="13" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -5450,35 +5450,35 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32869</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00164607</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
         <v>0</v>
@@ -5487,27 +5487,27 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32869</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00164607</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="O67" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>245</v>
       </c>
       <c r="P67" s="13" t="n">
         <v>0</v>
@@ -5559,12 +5559,12 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
@@ -5610,16 +5610,16 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O68" s="17" t="n">
         <v>0</v>
@@ -5631,32 +5631,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5671,44 +5671,44 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>705</v>
-      </c>
-      <c r="O69" s="13" t="n">
-        <v>1057.5</v>
+        <v>900</v>
+      </c>
+      <c r="O69" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P69" s="13" t="n">
-        <v>192.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
@@ -5750,57 +5750,57 @@
         <v>3</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>705</v>
+        <v>1057.5</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0</v>
+        <v>192.27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -5822,37 +5822,37 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>2138.2</v>
-      </c>
-      <c r="O71" s="17" t="n">
-        <v>1375.2</v>
+        <v>564</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>705</v>
       </c>
       <c r="P71" s="13" t="n">
-        <v>229.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5882,69 +5882,69 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O72" s="17" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5954,32 +5954,32 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O73" s="17" t="n">
         <v>0</v>
@@ -5991,12 +5991,12 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
@@ -6042,19 +6042,19 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>552</v>
-      </c>
-      <c r="O74" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>373.5</v>
       </c>
       <c r="P74" s="16" t="n">
         <v>0</v>
@@ -6063,12 +6063,12 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6103,59 +6103,59 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O75" s="13" t="n">
-        <v>142.1</v>
+        <v>548.4</v>
+      </c>
+      <c r="O75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>142.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
@@ -6170,32 +6170,32 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>1868</v>
+        <v>552</v>
       </c>
       <c r="O76" s="17" t="n">
         <v>0</v>
@@ -6207,27 +6207,27 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6247,64 +6247,64 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>882.5</v>
-      </c>
-      <c r="O77" s="17" t="n">
-        <v>0</v>
+        <v>142.1</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>142.1</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6314,34 +6314,34 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>1868</v>
+      </c>
+      <c r="O78" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
@@ -6351,32 +6351,32 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6386,64 +6386,64 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>450</v>
+        <v>882.5</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>450</v>
+        <v>882.5</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>0</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
@@ -6463,55 +6463,59 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>8.5</v>
+        <v>1.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O80" s="17" t="n">
-        <v>637</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>74.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr"/>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6531,64 +6535,64 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>765</v>
+        <v>450</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>892.5</v>
+        <v>450</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>187.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6598,64 +6602,60 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>1.25</v>
+        <v>8.5</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>300</v>
+        <v>1046.5</v>
+      </c>
+      <c r="O82" s="17" t="n">
+        <v>637</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>240</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6670,64 +6670,64 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.75</v>
+        <v>4.75</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>407</v>
-      </c>
-      <c r="O83" s="17" t="n">
-        <v>0</v>
+        <v>765</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>892.5</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>0</v>
+        <v>187.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6747,64 +6747,64 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>257.15</v>
-      </c>
-      <c r="O84" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O84" s="16" t="n">
+        <v>300</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6819,27 +6819,27 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>440.38</v>
+        <v>407</v>
       </c>
       <c r="O85" s="17" t="n">
         <v>0</v>
@@ -6851,12 +6851,12 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6886,32 +6886,32 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>285</v>
+        <v>257.15</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6923,12 +6923,12 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6958,35 +6958,35 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>120</v>
+        <v>440.38</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
         <v>0</v>
@@ -6995,27 +6995,27 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7046,16 +7046,16 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="O88" s="17" t="n">
         <v>0</v>
@@ -7067,32 +7067,32 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
@@ -7118,19 +7118,19 @@
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>367.5</v>
+        <v>120</v>
       </c>
       <c r="P89" s="13" t="n">
         <v>0</v>
@@ -7139,27 +7139,27 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7174,64 +7174,64 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="O90" s="17" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7246,35 +7246,35 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O91" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>367.5</v>
       </c>
       <c r="P91" s="13" t="n">
         <v>0</v>
@@ -7283,27 +7283,27 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7323,64 +7323,64 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K92" s="15" t="n">
         <v>1</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7390,94 +7390,102 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>1500</v>
+        <v>203.5</v>
       </c>
       <c r="O93" s="17" t="n">
-        <v>214.9</v>
+        <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
-        <v>85.95999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L94" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N94" s="16" t="n">
         <v>0</v>
       </c>
@@ -7491,32 +7499,32 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -7526,49 +7534,49 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>322.35</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>0</v>
+        <v>128.94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7578,12 +7586,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7593,7 +7601,7 @@
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
@@ -7603,25 +7611,17 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M96" s="15" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L96" s="15" t="inlineStr"/>
+      <c r="M96" s="15" t="inlineStr"/>
       <c r="N96" s="16" t="n">
         <v>0</v>
       </c>
@@ -7635,12 +7635,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
@@ -7675,29 +7675,29 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O97" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="13" t="n">
@@ -7707,32 +7707,32 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -7747,23 +7747,23 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
@@ -7779,32 +7779,32 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7814,64 +7814,64 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="13" t="n">
-        <v>28.1</v>
+        <v>210</v>
+      </c>
+      <c r="O99" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>18.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7886,34 +7886,34 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="O100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7923,32 +7923,32 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7958,49 +7958,49 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>255</v>
-      </c>
-      <c r="O101" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>28.1</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8035,27 +8035,27 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="O102" s="17" t="n">
         <v>0</v>
@@ -8067,12 +8067,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -8107,27 +8107,27 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O103" s="17" t="n">
         <v>0</v>
@@ -8139,27 +8139,27 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
@@ -8190,16 +8190,16 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="O104" s="17" t="n">
         <v>0</v>
@@ -8211,32 +8211,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8246,34 +8246,34 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="O105" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8283,32 +8283,32 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
@@ -8318,32 +8318,32 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="O106" s="17" t="n">
         <v>0</v>
@@ -8355,27 +8355,27 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -8395,23 +8395,23 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8427,32 +8427,32 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
@@ -8462,34 +8462,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8499,12 +8499,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -8539,23 +8539,23 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0.92</v>
+        <v>7</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
@@ -8571,32 +8571,32 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8606,28 +8606,28 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8715,32 +8715,32 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8750,28 +8750,28 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>4.5</v>
+        <v>0.92</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8787,26 +8787,28 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8825,29 +8827,29 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8857,27 +8859,27 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>Commune de Calais</t>
         </is>
       </c>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
@@ -8892,28 +8894,28 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8929,32 +8931,30 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v/>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -8964,67 +8964,69 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="13" t="n">
-        <v>405</v>
+        <v>157.5</v>
+      </c>
+      <c r="O115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9034,69 +9036,69 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O116" s="17" t="n">
-        <v>450.42</v>
+        <v>0</v>
+      </c>
+      <c r="O116" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>150.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9106,49 +9108,49 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>392.5</v>
-      </c>
-      <c r="O117" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O117" s="13" t="n">
+        <v>405</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9158,13 +9160,11 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v/>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9183,33 +9183,33 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>1556.25</v>
-      </c>
-      <c r="O118" s="17" t="n">
-        <v>0</v>
+        <v>2812.32</v>
+      </c>
+      <c r="O118" s="16" t="n">
+        <v>3453.22</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0</v>
+        <v>1151.07</v>
       </c>
     </row>
     <row r="119">
@@ -9266,16 +9266,16 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>1790</v>
+        <v>392.5</v>
       </c>
       <c r="O119" s="17" t="n">
         <v>0</v>
@@ -9338,18 +9338,18 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>1556.25</v>
+      </c>
+      <c r="O120" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9410,18 +9410,18 @@
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O121" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9431,12 +9431,12 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -9446,11 +9446,13 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
@@ -9464,28 +9466,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>4.25</v>
+        <v>1.15</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9501,12 +9503,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -9516,11 +9518,13 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
@@ -9539,29 +9543,29 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>3</v>
+        <v>1.15</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>732</v>
-      </c>
-      <c r="O123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9571,12 +9575,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9586,34 +9590,48 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F124" s="15" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H124" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L124" s="15" t="inlineStr"/>
-      <c r="M124" s="15" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N124" s="16" t="n">
         <v>0</v>
       </c>
@@ -9627,12 +9645,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9642,7 +9660,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9660,102 +9678,86 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="13" t="n">
-        <v>230</v>
+        <v>732</v>
+      </c>
+      <c r="O125" s="17" t="n">
+        <v>640</v>
       </c>
       <c r="P125" s="13" t="n">
-        <v>184</v>
+        <v>213.33</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+          <t>CD74</t>
         </is>
       </c>
       <c r="E126" s="15" t="inlineStr">
         <is>
-          <t>Déploiement LiEx</t>
-        </is>
-      </c>
-      <c r="F126" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="inlineStr"/>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr"/>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-26783</t>
-        </is>
-      </c>
-      <c r="M126" s="15" t="inlineStr">
-        <is>
-          <t>00142659</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr"/>
+      <c r="M126" s="15" t="inlineStr"/>
       <c r="N126" s="16" t="n">
         <v>0</v>
       </c>
@@ -9769,12 +9771,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9784,7 +9786,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9802,63 +9804,65 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O127" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>230</v>
       </c>
       <c r="P127" s="13" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
@@ -9872,28 +9876,28 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
@@ -9909,22 +9913,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9942,34 +9946,34 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O129" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="13" t="n">
@@ -9979,22 +9983,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10012,28 +10016,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>3.62</v>
+        <v>2</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10049,12 +10053,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10064,7 +10068,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10082,28 +10086,28 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>3.62</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
@@ -10119,22 +10123,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10157,29 +10161,29 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>4.75</v>
+        <v>3.62</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10189,22 +10193,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10212,7 +10216,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -10222,34 +10226,34 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
-        <v>964.1</v>
-      </c>
-      <c r="O133" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10259,22 +10263,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10282,7 +10286,7 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -10292,35 +10296,35 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
-        <v>140.4</v>
+        <v>2323</v>
       </c>
       <c r="O134" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
         <v>0</v>
@@ -10329,22 +10333,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10352,7 +10356,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -10362,34 +10366,34 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="13" t="n">
+        <v>964.1</v>
+      </c>
+      <c r="O135" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
@@ -10399,17 +10403,17 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
@@ -10422,7 +10426,7 @@
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
@@ -10437,30 +10441,30 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O136" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P136" s="16" t="n">
         <v>0</v>
@@ -10469,12 +10473,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10484,7 +10488,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10507,23 +10511,23 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.19</v>
+        <v>1</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10539,22 +10543,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10572,28 +10576,28 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.19</v>
+        <v>2</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10624,7 +10628,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10658,12 +10662,12 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
@@ -10728,12 +10732,12 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
@@ -10749,12 +10753,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10782,28 +10786,28 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
@@ -10819,22 +10823,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10852,28 +10856,28 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
@@ -10889,22 +10893,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10912,7 +10916,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -10927,29 +10931,29 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10959,18 +10963,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C144" s="15" t="inlineStr"/>
+          <t>[Grand Dax] - Pastell</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10993,30 +11001,30 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O144" s="16" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
         <v>0</v>
@@ -11025,22 +11033,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11048,7 +11056,7 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -11058,34 +11066,34 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" s="13" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O145" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="13" t="n">
@@ -11095,22 +11103,18 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
-        </is>
-      </c>
-      <c r="C146" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr"/>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11133,30 +11137,30 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O146" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O146" s="16" t="n">
+        <v>575</v>
       </c>
       <c r="P146" s="16" t="n">
         <v>0</v>
@@ -11165,12 +11169,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11180,7 +11184,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11198,34 +11202,34 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="13" t="n">
@@ -11235,12 +11239,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11250,7 +11254,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11266,24 +11270,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H148" s="15" t="inlineStr"/>
+      <c r="H148" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L148" s="15" t="inlineStr"/>
-      <c r="M148" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L148" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M148" s="15" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N148" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O148" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P148" s="16" t="n">
@@ -11293,12 +11309,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11308,7 +11324,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11326,34 +11342,34 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O149" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="13" t="n">
@@ -11363,22 +11379,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11394,32 +11410,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H150" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H150" s="15" t="inlineStr"/>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M150" s="15" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr"/>
+      <c r="M150" s="15" t="inlineStr"/>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
@@ -11433,12 +11437,12 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
@@ -11448,7 +11452,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11471,23 +11475,23 @@
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
@@ -11503,12 +11507,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11518,7 +11522,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11536,28 +11540,28 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
@@ -11573,22 +11577,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11601,27 +11605,35 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11635,12 +11647,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11650,7 +11662,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11663,7 +11675,7 @@
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H154" s="15" t="inlineStr">
@@ -11673,17 +11685,25 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr"/>
-      <c r="M154" s="15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M154" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N154" s="16" t="n">
         <v>0</v>
       </c>
@@ -11697,22 +11717,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11720,7 +11740,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11730,7 +11750,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -11742,7 +11762,7 @@
         <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11759,22 +11779,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11782,44 +11802,36 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M156" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>5.25</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr"/>
+      <c r="M156" s="15" t="inlineStr"/>
       <c r="N156" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P156" s="16" t="n">
@@ -11829,22 +11841,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11852,40 +11864,32 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="L157" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M157" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L157" s="12" t="inlineStr"/>
+      <c r="M157" s="12" t="inlineStr"/>
       <c r="N157" s="13" t="n">
         <v>0</v>
       </c>
@@ -11899,22 +11903,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11922,7 +11926,7 @@
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
@@ -11932,34 +11936,34 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O158" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P158" s="16" t="n">
@@ -11969,22 +11973,22 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11992,32 +11996,40 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr"/>
-      <c r="M159" s="12" t="inlineStr"/>
+        <v>3.62</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N159" s="13" t="n">
         <v>0</v>
       </c>
@@ -12031,22 +12043,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12059,7 +12071,7 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
@@ -12069,17 +12081,25 @@
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr"/>
-      <c r="M160" s="15" t="inlineStr"/>
+        <v>3.62</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M160" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
@@ -12093,22 +12113,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-17117</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>NÎMES</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12131,30 +12151,30 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28005</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>448204</t>
         </is>
       </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="P161" s="13" t="n">
         <v>0</v>
@@ -12163,22 +12183,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12186,7 +12206,7 @@
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G162" s="15" t="inlineStr">
@@ -12196,19 +12216,19 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12225,12 +12245,12 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
@@ -12240,7 +12260,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12263,14 +12283,14 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12287,12 +12307,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12302,7 +12322,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12315,7 +12335,7 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
@@ -12325,17 +12345,25 @@
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr"/>
-      <c r="M164" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M164" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N164" s="16" t="n">
         <v>0</v>
       </c>
@@ -12349,22 +12377,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12382,19 +12410,19 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>7.25</v>
+        <v>2.5</v>
       </c>
       <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
@@ -12411,22 +12439,22 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12449,14 +12477,14 @@
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12473,12 +12501,12 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
@@ -12488,7 +12516,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12501,7 +12529,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -12511,25 +12539,17 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L167" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M167" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L167" s="12" t="inlineStr"/>
+      <c r="M167" s="12" t="inlineStr"/>
       <c r="N167" s="13" t="n">
         <v>0</v>
       </c>
@@ -12543,12 +12563,12 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
@@ -12558,7 +12578,7 @@
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12571,20 +12591,24 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H168" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H168" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12601,22 +12625,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12634,25 +12658,21 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
       <c r="N169" s="13" t="n">
         <v>0</v>
@@ -12667,22 +12687,22 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12695,27 +12715,35 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr"/>
-      <c r="M170" s="15" t="inlineStr"/>
+        <v>10.25</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M170" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12729,28 +12757,26 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v/>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
@@ -12759,17 +12785,13 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr"/>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
@@ -12793,28 +12815,26 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E172" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v/>
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
@@ -12828,21 +12848,25 @@
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M172" s="15" t="inlineStr"/>
       <c r="N172" s="16" t="n">
         <v>0</v>
@@ -12857,24 +12881,26 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C173" s="12" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E173" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v/>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
@@ -12893,14 +12919,14 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -12917,21 +12943,29 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C174" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E174" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12939,35 +12973,31 @@
       </c>
       <c r="G174" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H174" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M174" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L174" s="15" t="inlineStr"/>
+      <c r="M174" s="15" t="inlineStr"/>
       <c r="N174" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P174" s="16" t="n">
@@ -12977,21 +13007,29 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="C175" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="E175" s="12" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12999,35 +13037,31 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H175" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M175" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
+        <v>9.25</v>
+      </c>
+      <c r="L175" s="12" t="inlineStr"/>
+      <c r="M175" s="12" t="inlineStr"/>
       <c r="N175" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O175" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P175" s="13" t="n">
@@ -13037,21 +13071,25 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr"/>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
-        </is>
-      </c>
-      <c r="E176" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13059,20 +13097,24 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H176" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H176" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L176" s="15" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
@@ -13089,18 +13131,18 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13111,27 +13153,35 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr"/>
-      <c r="M177" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N177" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O177" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P177" s="13" t="n">
@@ -13141,18 +13191,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13163,28 +13213,36 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr"/>
-      <c r="M178" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33167</t>
+        </is>
+      </c>
+      <c r="M178" s="15" t="inlineStr">
+        <is>
+          <t>00165437</t>
+        </is>
+      </c>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O178" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P178" s="16" t="n">
         <v>0</v>
@@ -13193,18 +13251,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13215,59 +13273,275 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="J179" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
+      <c r="N179" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1182</t>
+        </is>
+      </c>
+      <c r="B180" s="15" t="inlineStr">
+        <is>
+          <t>Commune de La Ville aux Dames</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr"/>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>Commune de La Ville aux Dames</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="inlineStr"/>
+      <c r="F180" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G180" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H180" s="15" t="inlineStr"/>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="J180" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K180" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L180" s="15" t="inlineStr"/>
+      <c r="M180" s="15" t="inlineStr"/>
+      <c r="N180" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1126</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CARRY LE ROUET</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr"/>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CARRY LE ROUET</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="inlineStr"/>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H181" s="12" t="inlineStr"/>
+      <c r="I181" s="12" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="J181" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K181" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L181" s="12" t="inlineStr"/>
+      <c r="M181" s="12" t="inlineStr"/>
+      <c r="N181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1021</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr"/>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr"/>
+      <c r="F182" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G182" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="inlineStr"/>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J182" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K182" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L182" s="15" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
+      <c r="N182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr"/>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr"/>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr"/>
+      <c r="I183" s="12" t="inlineStr">
+        <is>
           <t>20/03/2025</t>
         </is>
       </c>
-      <c r="J179" s="12" t="n">
+      <c r="J183" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K179" s="12" t="n">
+      <c r="K183" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L179" s="12" t="inlineStr"/>
-      <c r="M179" s="12" t="inlineStr"/>
-      <c r="N179" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O179" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="18" t="inlineStr">
+      <c r="L183" s="12" t="inlineStr"/>
+      <c r="M183" s="12" t="inlineStr"/>
+      <c r="N183" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B180" s="18" t="inlineStr"/>
-      <c r="C180" s="18" t="inlineStr"/>
-      <c r="D180" s="18" t="inlineStr"/>
-      <c r="E180" s="18" t="inlineStr"/>
-      <c r="F180" s="18" t="inlineStr"/>
-      <c r="G180" s="18" t="inlineStr"/>
-      <c r="H180" s="18" t="inlineStr"/>
-      <c r="I180" s="18" t="inlineStr"/>
-      <c r="J180" s="18" t="inlineStr"/>
-      <c r="K180" s="18" t="inlineStr"/>
-      <c r="L180" s="18" t="inlineStr"/>
-      <c r="M180" s="18" t="inlineStr"/>
-      <c r="N180" s="19" t="n">
+      <c r="B184" s="18" t="inlineStr"/>
+      <c r="C184" s="18" t="inlineStr"/>
+      <c r="D184" s="18" t="inlineStr"/>
+      <c r="E184" s="18" t="inlineStr"/>
+      <c r="F184" s="18" t="inlineStr"/>
+      <c r="G184" s="18" t="inlineStr"/>
+      <c r="H184" s="18" t="inlineStr"/>
+      <c r="I184" s="18" t="inlineStr"/>
+      <c r="J184" s="18" t="inlineStr"/>
+      <c r="K184" s="18" t="inlineStr"/>
+      <c r="L184" s="18" t="inlineStr"/>
+      <c r="M184" s="18" t="inlineStr"/>
+      <c r="N184" s="19" t="n">
         <v>69305.66</v>
       </c>
-      <c r="O180" s="19" t="n">
-        <v>40329.97</v>
-      </c>
-      <c r="P180" s="19" t="n">
-        <v>133.99</v>
+      <c r="O184" s="19" t="n">
+        <v>48923.66500000001</v>
+      </c>
+      <c r="P184" s="19" t="n">
+        <v>162.54</v>
       </c>
     </row>
   </sheetData>
@@ -13448,6 +13722,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId179"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14513,22 +14791,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>385298</v>
+        <v>376704</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>198461</v>
+        <v>106769</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>186837</v>
+        <v>269935</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>149530</v>
+        <v>197138</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>15389</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="6">
@@ -14538,22 +14816,22 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>181856</v>
+        <v>174896</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>75147</v>
+        <v>62797</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106709</v>
+        <v>112098</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>92411</v>
+        <v>98334</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4238</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="7">
@@ -14563,16 +14841,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>203442</v>
+        <v>201809</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>123314</v>
+        <v>43971</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>80128</v>
+        <v>157837</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>57120</v>
+        <v>98804</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>11857</v>

--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>48,924 €</t>
+          <t>49,584 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>30,914 €</t>
+          <t>31,574 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -11379,22 +11379,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20217</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>CAP ATLANTIQUE</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
@@ -11410,25 +11410,37 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H150" s="15" t="inlineStr"/>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr"/>
-      <c r="M150" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28028</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>464365</t>
+        </is>
+      </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="P150" s="16" t="n">
         <v>0</v>
@@ -11437,22 +11449,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11468,32 +11480,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H151" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11507,12 +11507,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11540,28 +11540,28 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
@@ -11577,12 +11577,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11610,28 +11610,28 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
@@ -11647,12 +11647,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11685,23 +11685,23 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
@@ -11717,22 +11717,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11745,27 +11745,35 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K155" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="L155" s="12" t="inlineStr"/>
-      <c r="M155" s="12" t="inlineStr"/>
+      <c r="L155" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
@@ -11779,22 +11787,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11812,7 +11820,7 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
@@ -11824,7 +11832,7 @@
         <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>5.25</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11841,22 +11849,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11864,7 +11872,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -11886,7 +11894,7 @@
         <v>19</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11903,12 +11911,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11918,7 +11926,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11931,39 +11939,31 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M158" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr"/>
+      <c r="M158" s="15" t="inlineStr"/>
       <c r="N158" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O158" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P158" s="16" t="n">
@@ -11973,22 +11973,22 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -12006,34 +12006,34 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N159" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O159" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P159" s="13" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
@@ -12113,22 +12113,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-17117</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>NÎMES</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12151,30 +12151,30 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>14/10/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28005</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>448204</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="P161" s="13" t="n">
         <v>0</v>
@@ -12183,22 +12183,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17117</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>NÎMES</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12206,37 +12206,45 @@
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L162" s="15" t="inlineStr"/>
-      <c r="M162" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28005</t>
+        </is>
+      </c>
+      <c r="M162" s="15" t="inlineStr">
+        <is>
+          <t>448204</t>
+        </is>
+      </c>
       <c r="N162" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O162" s="16" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="P162" s="16" t="n">
         <v>0</v>
@@ -12245,22 +12253,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12268,7 +12276,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -12278,19 +12286,19 @@
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>0.25</v>
+        <v>4.75</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12307,22 +12315,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12335,7 +12343,7 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
@@ -12345,25 +12353,17 @@
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M164" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
       <c r="N164" s="16" t="n">
         <v>0</v>
       </c>
@@ -12377,12 +12377,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -12415,17 +12415,25 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L165" s="12" t="inlineStr"/>
-      <c r="M165" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L165" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M165" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N165" s="13" t="n">
         <v>0</v>
       </c>
@@ -12439,22 +12447,22 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12477,14 +12485,14 @@
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12501,22 +12509,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12539,14 +12547,14 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12563,22 +12571,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12596,19 +12604,19 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>7.25</v>
+        <v>1.25</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12625,22 +12633,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12658,19 +12666,19 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>0.25</v>
+        <v>7.25</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12687,12 +12695,12 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -12702,7 +12710,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12715,7 +12723,7 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
@@ -12725,25 +12733,17 @@
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12757,22 +12757,22 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12788,20 +12788,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H171" s="12" t="inlineStr"/>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr"/>
-      <c r="M171" s="12" t="inlineStr"/>
+        <v>10.25</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12815,12 +12827,12 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
@@ -12830,7 +12842,7 @@
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12843,30 +12855,22 @@
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H172" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H172" s="15" t="inlineStr"/>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
       <c r="N172" s="16" t="n">
         <v>0</v>
@@ -12881,12 +12885,12 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
@@ -12896,7 +12900,7 @@
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -12919,16 +12923,20 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M173" s="12" t="inlineStr"/>
       <c r="N173" s="13" t="n">
         <v>0</v>
@@ -12943,28 +12951,26 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E174" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v/>
       </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
@@ -12990,7 +12996,7 @@
         <v>34</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -13007,12 +13013,12 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -13022,12 +13028,12 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -13042,7 +13048,7 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I175" s="12" t="inlineStr">
@@ -13054,7 +13060,7 @@
         <v>34</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>9.25</v>
+        <v>0.5</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13071,23 +13077,27 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C176" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C176" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
@@ -13102,19 +13112,19 @@
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>1.75</v>
+        <v>9.25</v>
       </c>
       <c r="L176" s="15" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
@@ -13131,21 +13141,25 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E177" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13153,35 +13167,31 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H177" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M177" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr"/>
       <c r="N177" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O177" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P177" s="13" t="n">
@@ -13191,18 +13201,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13219,30 +13229,30 @@
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K178" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L178" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33167</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M178" s="15" t="inlineStr">
         <is>
-          <t>00165437</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N178" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" s="16" t="n">
-        <v>100</v>
+        <v>510.6</v>
+      </c>
+      <c r="O178" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P178" s="16" t="n">
         <v>0</v>
@@ -13251,18 +13261,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13279,7 +13289,7 @@
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
@@ -13290,19 +13300,19 @@
       </c>
       <c r="L179" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M179" s="12" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N179" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O179" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O179" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="P179" s="13" t="n">
         <v>0</v>
@@ -13311,18 +13321,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13333,27 +13343,35 @@
       </c>
       <c r="G180" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L180" s="15" t="inlineStr"/>
-      <c r="M180" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L180" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M180" s="15" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N180" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="O180" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P180" s="16" t="n">
@@ -13363,18 +13381,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13391,14 +13409,14 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13415,18 +13433,18 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr"/>
@@ -13443,14 +13461,14 @@
       <c r="H182" s="15" t="inlineStr"/>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13467,18 +13485,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1021</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13495,11 +13513,11 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K183" s="12" t="n">
         <v>0.5</v>
@@ -13517,31 +13535,83 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="18" t="inlineStr">
+      <c r="A184" s="14" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C184" s="15" t="inlineStr"/>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr"/>
+      <c r="F184" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr"/>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J184" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K184" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L184" s="15" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
+      <c r="N184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B184" s="18" t="inlineStr"/>
-      <c r="C184" s="18" t="inlineStr"/>
-      <c r="D184" s="18" t="inlineStr"/>
-      <c r="E184" s="18" t="inlineStr"/>
-      <c r="F184" s="18" t="inlineStr"/>
-      <c r="G184" s="18" t="inlineStr"/>
-      <c r="H184" s="18" t="inlineStr"/>
-      <c r="I184" s="18" t="inlineStr"/>
-      <c r="J184" s="18" t="inlineStr"/>
-      <c r="K184" s="18" t="inlineStr"/>
-      <c r="L184" s="18" t="inlineStr"/>
-      <c r="M184" s="18" t="inlineStr"/>
-      <c r="N184" s="19" t="n">
+      <c r="B185" s="18" t="inlineStr"/>
+      <c r="C185" s="18" t="inlineStr"/>
+      <c r="D185" s="18" t="inlineStr"/>
+      <c r="E185" s="18" t="inlineStr"/>
+      <c r="F185" s="18" t="inlineStr"/>
+      <c r="G185" s="18" t="inlineStr"/>
+      <c r="H185" s="18" t="inlineStr"/>
+      <c r="I185" s="18" t="inlineStr"/>
+      <c r="J185" s="18" t="inlineStr"/>
+      <c r="K185" s="18" t="inlineStr"/>
+      <c r="L185" s="18" t="inlineStr"/>
+      <c r="M185" s="18" t="inlineStr"/>
+      <c r="N185" s="19" t="n">
         <v>69305.66</v>
       </c>
-      <c r="O184" s="19" t="n">
-        <v>48923.66500000001</v>
-      </c>
-      <c r="P184" s="19" t="n">
-        <v>162.54</v>
+      <c r="O185" s="19" t="n">
+        <v>49583.66500000001</v>
+      </c>
+      <c r="P185" s="19" t="n">
+        <v>164.73</v>
       </c>
     </row>
   </sheetData>
@@ -13726,6 +13796,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14791,16 +14862,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>376704</v>
+        <v>376044</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>106769</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>269935</v>
+        <v>269275</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>197138</v>
+        <v>196478</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -14841,16 +14912,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>201809</v>
+        <v>201149</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>43971</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>157837</v>
+        <v>157177</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>98804</v>
+        <v>98144</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>11857</v>

--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>49,584 €</t>
+          <t>50,020 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>18,010 €</t>
+          <t>18,446 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -2046,10 +2046,10 @@
         <v>1296</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>2016</v>
+        <v>2232</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>146.62</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="19">
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32">
@@ -13608,10 +13608,10 @@
         <v>69305.66</v>
       </c>
       <c r="O185" s="19" t="n">
-        <v>49583.66500000001</v>
+        <v>50019.66500000001</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>164.73</v>
+        <v>166.18</v>
       </c>
     </row>
   </sheetData>
@@ -14862,16 +14862,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>376044</v>
+        <v>375608</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>106769</v>
+        <v>106553</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>269275</v>
+        <v>269055</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>196478</v>
+        <v>196258</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -14887,16 +14887,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>174896</v>
+        <v>174460</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>62797</v>
+        <v>62581</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>112098</v>
+        <v>111878</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>98334</v>
+        <v>98114</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>

--- a/jira_export_2026-07-24.xlsx
+++ b/jira_export_2026-07-24.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>50,020 €</t>
+          <t>50,209 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>18,446 €</t>
+          <t>18,635 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -3326,10 +3326,10 @@
         <v>1890</v>
       </c>
       <c r="O36" s="17" t="n">
-        <v>1512</v>
+        <v>1701</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>504</v>
+        <v>567</v>
       </c>
     </row>
     <row r="37">
@@ -13608,10 +13608,10 @@
         <v>69305.66</v>
       </c>
       <c r="O185" s="19" t="n">
-        <v>50019.66500000001</v>
+        <v>50208.66500000001</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>166.18</v>
+        <v>166.81</v>
       </c>
     </row>
   </sheetData>
@@ -14862,10 +14862,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>375608</v>
+        <v>375419</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>106553</v>
+        <v>106364</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>269055</v>
@@ -14887,10 +14887,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>174460</v>
+        <v>174271</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>62581</v>
+        <v>62392</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>111878</v>
